--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 13:21</t>
+          <t>更新时间: 2026-09-13 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 13:38</t>
+          <t>更新时间: 2026-09-14 13:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 13:43</t>
+          <t>更新时间: 2026-09-15 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 13:44</t>
+          <t>更新时间: 2026-09-16 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 13:36</t>
+          <t>更新时间: 2026-09-17 13:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 13:41</t>
+          <t>更新时间: 2026-09-18 13:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 13:30</t>
+          <t>更新时间: 2026-09-19 13:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 13:28</t>
+          <t>更新时间: 2026-09-20 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 13:40</t>
+          <t>更新时间: 2026-09-21 13:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 13:50</t>
+          <t>更新时间: 2026-09-22 13:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 13:48</t>
+          <t>更新时间: 2026-09-23 13:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 13:27</t>
+          <t>更新时间: 2026-09-24 13:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 13:48</t>
+          <t>更新时间: 2026-09-25 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 13:44</t>
+          <t>更新时间: 2026-09-26 13:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:48</t>
+          <t>更新时间: 2026-09-27 14:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 14:08</t>
+          <t>更新时间: 2026-09-28 14:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 14:17</t>
+          <t>更新时间: 2026-09-29 14:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 14:32</t>
+          <t>更新时间: 2026-09-30 14:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 14:16</t>
+          <t>更新时间: 2026-10-01 14:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 14:47</t>
+          <t>更新时间: 2026-10-02 14:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 14:38</t>
+          <t>更新时间: 2026-10-03 14:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 14:00</t>
+          <t>更新时间: 2026-10-04 14:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 14:36</t>
+          <t>更新时间: 2026-10-05 14:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 14:31</t>
+          <t>更新时间: 2026-10-06 15:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 15:08</t>
+          <t>更新时间: 2026-10-07 14:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 14:48</t>
+          <t>更新时间: 2026-10-08 14:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 14:57</t>
+          <t>更新时间: 2026-10-09 15:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 15:08</t>
+          <t>更新时间: 2026-10-10 14:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 14:39</t>
+          <t>更新时间: 2026-10-11 14:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 14:46</t>
+          <t>更新时间: 2026-10-12 14:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 14:54</t>
+          <t>更新时间: 2026-10-13 15:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 15:19</t>
+          <t>更新时间: 2026-10-14 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 13:44</t>
+          <t>更新时间: 2026-10-15 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-15 13:31</t>
+          <t>更新时间: 2026-10-16 13:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-16 13:22</t>
+          <t>更新时间: 2026-10-17 13:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-17 13:16</t>
+          <t>更新时间: 2026-10-18 13:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 13:22</t>
+          <t>更新时间: 2026-10-19 13:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-19 13:39</t>
+          <t>更新时间: 2026-10-20 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-20 13:38</t>
+          <t>更新时间: 2026-10-21 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-21 13:40</t>
+          <t>更新时间: 2026-10-22 13:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 13:43</t>
+          <t>更新时间: 2026-10-23 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-23 13:44</t>
+          <t>更新时间: 2026-10-24 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-24 13:20</t>
+          <t>更新时间: 2026-10-25 13:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-25 13:37</t>
+          <t>更新时间: 2026-10-26 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-26 13:44</t>
+          <t>更新时间: 2026-10-27 13:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 13:56</t>
+          <t>更新时间: 2026-10-28 14:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 14:35</t>
+          <t>更新时间: 2026-10-29 14:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 14:45</t>
+          <t>更新时间: 2026-10-30 14:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 14:44</t>
+          <t>更新时间: 2026-10-31 14:35</t>
         </is>
       </c>
     </row>
